--- a/Data/Home/Kitchen.CookerHood001.xlsx
+++ b/Data/Home/Kitchen.CookerHood001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709792638</v>
+        <v>1711928183</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709793153</v>
+        <v>1711930053</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -541,6 +547,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1711075969</v>
+        <v>1712274814</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -577,6 +584,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1711077801</v>
+        <v>1712275901</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -613,6 +621,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1711515202</v>
+        <v>1712306599</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -649,6 +658,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,7 +677,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1711516716</v>
+        <v>1712308939</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,6 +695,1043 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1712374268</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: on</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1712378351</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: off</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1712551678</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: on</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1712555427</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: off</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1712792002</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: on</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1712795260</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: off</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1712905757</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: on</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1712908839</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: off</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1713019488</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: on</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1713023246</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: off</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1713111900</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: on</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1713114767</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: off</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1713138443</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: on</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1713140111</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: off</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1713344164</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: on</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1713345026</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: off</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1713600341</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: on</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1713602231</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: off</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1713945240</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: on</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1713947178</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: off</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1714021963</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: on</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1714025873</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: off</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1714088538</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: on</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1714091247</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: off</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1714192706</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: on</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1714194188</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: off</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1714290156</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: on</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CookerHood_Operation</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1714291829</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Kitchen.CookerHood001.state: off</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
